--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -1,46 +1,248 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10601002\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F439064E-F1FD-4089-8440-FF65A66C02BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vocabulary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Vocabulary" sheetId="1" r:id="rId1"/>
+    <sheet name="說明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Chinese</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>example_zh</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>規則</t>
+  </si>
+  <si>
+    <t>內容</t>
+  </si>
+  <si>
+    <t>工作表名稱</t>
+  </si>
+  <si>
+    <t>Vocabulary</t>
+  </si>
+  <si>
+    <t>必填欄位</t>
+  </si>
+  <si>
+    <t>ID、English、Chinese</t>
+  </si>
+  <si>
+    <t>每列唯一且不要修改，用來保留手機的 Pass/Fail 紀錄</t>
+  </si>
+  <si>
+    <t>更新方式</t>
+  </si>
+  <si>
+    <t>儲存成 vocabulary.xlsx，覆蓋 GitHub 同名檔案</t>
+  </si>
+  <si>
+    <t>comply with</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Please comply with the rules.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>請遵守規則。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">遵守規定; 符合規定(合規) n.  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>This product is in compliance with international standards.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>此產品符合國際標準。</t>
+  </si>
+  <si>
+    <t>抱怨 n.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>complaint  [ei]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>compliance  [ai]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Please remain seated. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>remain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>請保持就座。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>word</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sentence</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>How's it going? ; How are you doing?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你好嗎?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">How's it going?   </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Good, thanks. How about you? ; It's going well. ; I' m doing well. (I'm good)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>word_comply</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>word_compliance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>word_complaint</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>word_remain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>保持 v.  ; (比較正式, 日常口語較少用)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sentence_howareyou</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>That's all for today. Thanks, everyone. ; Let's end the call here. Thanks, everyone.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>今天就到這裡，謝謝大家。; 我們今天通話就到這裡，謝謝大家。;(結束電話會議的說法)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sentence_endcall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sentence_dayoff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tom 今天請假。(最簡單、最常用)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom is off today. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遵守(規定) v.  ; (正式商務與法規用字; 日常比較常說follow the rules)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>complain 抱怨 v. ; complaint 抱怨 n.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">compliance 遵守規定, 符合規定(合規) n. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00315C4B"/>
+        <fgColor rgb="FF315C4B"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,100 +258,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="VocabularyTable" displayName="VocabularyTable" ref="A1:F4" headerRowCount="1">
-  <autoFilter ref="A1:F4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="VocabularyTable" displayName="VocabularyTable" ref="A1:F8">
+  <autoFilter ref="A1:F8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="English"/>
-    <tableColumn id="3" name="Chinese"/>
-    <tableColumn id="4" name="example"/>
-    <tableColumn id="5" name="example_zh"/>
-    <tableColumn id="6" name="category"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="English"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Chinese"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="example"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="example_zh"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="category"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium4" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -437,232 +581,226 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Chinese</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>example</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>example_zh</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>tech_install</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>install</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>安裝</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Please install the driver.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>請安裝驅動程式。</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>tech_verify</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>verify</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Verify the firmware version.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>確認韌體版本。</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>general_flexible</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>有彈性的</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>This workflow is flexible.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>這個流程很有彈性。</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="65" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>內容</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>工作表名稱</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>必填欄位</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ID、English、Chinese</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>每列唯一且不要修改，用來保留手機的 Pass/Fail 紀錄</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>更新方式</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>儲存成 vocabulary.xlsx，覆蓋 GitHub 同名檔案</t>
-        </is>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10601002\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F439064E-F1FD-4089-8440-FF65A66C02BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A33CC7-4ECA-4EEA-96E3-A87FC0B6BA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,10 +76,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>請遵守規則。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">遵守規定; 符合規定(合規) n.  </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -187,15 +183,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>遵守(規定) v.  ; (正式商務與法規用字; 日常比較常說follow the rules)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>complain 抱怨 v. ; complaint 抱怨 n.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">compliance 遵守規定, 符合規定(合規) n. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>請遵守規則。;  (正式商務與法規用字, 日常比較常說follow the rules)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">遵守(規定) v. </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -588,7 +588,7 @@
     <col min="1" max="1" width="22.140625" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="39" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="4" max="4" width="46.35546875" customWidth="1"/>
     <col min="5" max="5" width="29.7109375" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
@@ -615,130 +615,130 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>30</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
         <v>39</v>
       </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10601002\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A33CC7-4ECA-4EEA-96E3-A87FC0B6BA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3BF711-D86D-4854-8A05-9DE079D38C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,14 +91,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>complaint  [ei]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>compliance  [ai]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Please remain seated. </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -119,22 +111,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>How's it going? ; How are you doing?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>你好嗎?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">How's it going?   </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Good, thanks. How about you? ; It's going well. ; I' m doing well. (I'm good)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>word_comply</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -151,22 +127,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>保持 v.  ; (比較正式, 日常口語較少用)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>sentence_howareyou</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>That's all for today. Thanks, everyone. ; Let's end the call here. Thanks, everyone.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>今天就到這裡，謝謝大家。; 我們今天通話就到這裡，謝謝大家。;(結束電話會議的說法)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>sentence_endcall</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -183,19 +147,55 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>complain 抱怨 v. ; complaint 抱怨 n.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">compliance 遵守規定, 符合規定(合規) n. </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>請遵守規則。;  (正式商務與法規用字, 日常比較常說follow the rules)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">遵守(規定) v. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">complain 抱怨 v. ; complaint 抱怨 n.; compliance 遵守規定, 符合規定(合規) n. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>請遵守規則。; (正式商務與法規用字, 日常比較常說follow the rules)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Good, thanks. How about you? </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">你好嗎? </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>compliance  ; [ai]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>complaint  ; [ei]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>How's it going? It's going well. ; How are you doing? I'm doing well. (I'm good)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>How's it going? ; How are you doing? ; (如何回覆對方)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">That's all for today. Thanks, everyone.; (Let's end the call here.) </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>今天就到這裡，謝謝大家。; (我們今天通話就到這裡);</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(結束電話會議的說法)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>保持 v.  ; (比較正式, 日常口語較少用); 請保持就座。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -615,30 +615,30 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
@@ -650,95 +650,95 @@
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
         <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10601002\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3BF711-D86D-4854-8A05-9DE079D38C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF09333-A4D9-448E-8D4A-5E2962869A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="19050" windowHeight="11722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vocabulary" sheetId="1" r:id="rId1"/>
@@ -139,10 +139,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Tom 今天請假。(最簡單、最常用)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Tom is off today. </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -183,19 +179,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">That's all for today. Thanks, everyone.; (Let's end the call here.) </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>今天就到這裡，謝謝大家。; (我們今天通話就到這裡);</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>(結束電話會議的說法)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>保持 v.  ; (比較正式, 日常口語較少用); 請保持就座。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tom 今天請假。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>That's all for today.; Let's end the call here. Thanks, everyone.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>今天就到這裡; 我們今天通話就到這裡，謝謝大家。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -621,13 +621,13 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
         <v>24</v>
@@ -638,7 +638,7 @@
         <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
@@ -658,13 +658,13 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
@@ -678,7 +678,7 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
         <v>21</v>
@@ -695,16 +695,16 @@
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -715,13 +715,13 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -732,10 +732,10 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>

--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10601002\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10601002\Desktop\AI_topic\_script_backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF09333-A4D9-448E-8D4A-5E2962869A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0AB1E0-C6BA-4147-8FF5-E6F5EF7FA4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="19050" windowHeight="11722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vocabulary" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
@@ -171,10 +171,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>How's it going? It's going well. ; How are you doing? I'm doing well. (I'm good)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>How's it going? ; How are you doing? ; (如何回覆對方)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -196,6 +192,58 @@
   </si>
   <si>
     <t>今天就到這裡; 我們今天通話就到這裡，謝謝大家。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bullets = bullet points</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(這個黑點看起來像小子彈，所以叫 bullet。)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bullets; Can you summarize this in bullets?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>word_bullet</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>條列點、項目符號 (子彈) ; 可以用條列方式整理嗎？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>This issue happens randomly. ; This issue occurs randomly.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>這個問題是隨機發生的。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sentence_random</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>How's it going? (最近如何?); It's going well. ; How are you doing? (你最近好嗎?) ; I'm doing well. (I'm good)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The power went out.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>停電了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sentence_powerwentout</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>happen = 口語 ; occur = 書面/正式</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -258,13 +306,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -283,8 +334,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="VocabularyTable" displayName="VocabularyTable" ref="A1:F8">
-  <autoFilter ref="A1:F8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="VocabularyTable" displayName="VocabularyTable" ref="A1:F11">
+  <autoFilter ref="A1:F11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="English"/>
@@ -582,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="1"/>
@@ -678,7 +729,7 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
         <v>21</v>
@@ -695,7 +746,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
         <v>38</v>
@@ -704,7 +755,7 @@
         <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -715,13 +766,13 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
         <v>46</v>
       </c>
-      <c r="C7" t="s">
-        <v>47</v>
-      </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -735,9 +786,60 @@
         <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" t="s">
         <v>25</v>
       </c>
     </row>

--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10601002\Desktop\AI_topic\_script_backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0AB1E0-C6BA-4147-8FF5-E6F5EF7FA4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7149C1C6-037A-4F39-ADE2-8035CA0F6E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,23 +21,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="94">
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>Chinese</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>example_zh</t>
-  </si>
-  <si>
     <t>category</t>
   </si>
   <si>
@@ -72,10 +60,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Please comply with the rules.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">遵守規定; 符合規定(合規) n.  </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -91,18 +75,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Please remain seated. </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>remain</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>請保持就座。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>word</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -111,34 +87,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>word_comply</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>word_compliance</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>word_complaint</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>word_remain</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sentence_howareyou</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sentence_endcall</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sentence_dayoff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Tom is off today. </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -151,18 +99,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>請遵守規則。; (正式商務與法規用字, 日常比較常說follow the rules)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Good, thanks. How about you? </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">你好嗎? </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>compliance  ; [ai]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -171,79 +107,277 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>How's it going? ; How are you doing? ; (如何回覆對方)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(結束電話會議的說法)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>保持 v.  ; (比較正式, 日常口語較少用); 請保持就座。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Tom 今天請假。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>That's all for today.; Let's end the call here. Thanks, everyone.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>今天就到這裡; 我們今天通話就到這裡，謝謝大家。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bullets = bullet points</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(這個黑點看起來像小子彈，所以叫 bullet。)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bullets; Can you summarize this in bullets?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>word_bullet</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>條列點、項目符號 (子彈) ; 可以用條列方式整理嗎？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>This issue happens randomly. ; This issue occurs randomly.</t>
+    <t>The power went out.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>停電了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Can I get a Tax refund (for this/these) ? </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you offer Tax-free shopping? </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(這個/些) 我可以退稅嗎?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你們有提供免稅購物嗎? ; (問店家 退稅服務)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寄放行李</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>leave my bags ; hold my bags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Can I leave my bags here?; Can I leave my bags here after check-out?; Can I leave my bags here until 6 PM? </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>other</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>How's it going?; How are you doing?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(正式商務與法規用字, 日常比較常說follow the rules); Please comply with the rules.; 請遵守規則。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>That's all for today.; Let's end the call here.; Thanks, everyone.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(結束電話會議的說法); 今天就到這裡; 我們今天通話就到這裡; 謝謝大家。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>保持 v.; (比較正式, 日常口語較少用)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你好嗎? ; (最近如何? / 你最近好嗎?)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bullets = bullet points (這個黑點看起來像小子彈，所以叫 bullet。)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>happen (口語) ; occur (書面/正式)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我可以把行李放在這裡嗎？; 我(退房後)可以把行李寄放在這裡嗎; 我可以把行李寄存在這裡(到下午6點)嗎？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>phrase</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">What time is breakfast? </t>
+  </si>
+  <si>
+    <t>早餐是幾點？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">What time does breakfast end? </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Can you recommend some good restaurants nearby?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (不限於正式的 restaurant，小吃店、咖啡廳或一般用餐地點都包含在內)</t>
+  </si>
+  <si>
+    <t>我最晚可以幾點來拿行李？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>What's the latest I can pick up my luggage?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">pick up my luggage </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>領取行李</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>What do you recommend?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你推薦什麼？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">早餐幾點結束？(早餐供應到幾點) </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你可以推薦幾間附近不錯的餐廳嗎？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>leave my bags 和 hold my bags 都很口語。;(母語人士通常不會特別區分是背包、旅行袋還是行李箱。; 通常用 luggage 或 bags來統稱行李，很少特別說 suitcase，除非真的要強調是行李箱才用suitcase。)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Are there) any good restaurants nearby?; Any good places to eat nearby?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>附近有沒有什麼不錯的"餐廳"？; 不錯的"地方"可以吃飯？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bullets</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>This issue happens/occurs randomly.</t>
+  </si>
+  <si>
+    <t>happen/occur randomly</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Can you summarize this in bullets?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>English sentence</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>English word</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>這個問題是隨機發生的。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sentence_random</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>How's it going? (最近如何?); It's going well. ; How are you doing? (你最近好嗎?) ; I'm doing well. (I'm good)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The power went out.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>停電了。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sentence_powerwentout</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>happen = 口語 ; occur = 書面/正式</t>
+  </si>
+  <si>
+    <t>隨機發生</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以用條列方式整理嗎？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>條列點、項目符號 (子彈)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Please remain seated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">請保持就座。 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese word</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Good (I'm good), thanks. How about you? ; It's going well.; I'm doing well.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese sentence</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>comply</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>compliance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>complaint</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>howsitgoing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>endcall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dayoff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bullet</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>happenrandom</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>powerwentout</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>taxrefund</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>taxfree</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>recommend_place</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>recommend_restaurant</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>recommend_what</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakfast_time</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakfast_end</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>leave_bags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pickup_luggage</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -251,7 +385,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,12 +407,6 @@
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -306,13 +434,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -334,14 +461,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="VocabularyTable" displayName="VocabularyTable" ref="A1:F11">
-  <autoFilter ref="A1:F11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="VocabularyTable" displayName="VocabularyTable" ref="A1:G20">
+  <autoFilter ref="A1:G20" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="English"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Chinese"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="example"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="example_zh"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="English word"/>
+    <tableColumn id="10" xr3:uid="{DBD0EA8D-AF2A-4A92-8485-118A4491D572}" name="English sentence"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Chinese word"/>
+    <tableColumn id="11" xr3:uid="{EAF1D198-3EED-4D52-94FE-A7B8778EA63C}" name="Chinese sentence"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="other"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="category"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -633,214 +761,362 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="39" customWidth="1"/>
-    <col min="4" max="4" width="46.35546875" customWidth="1"/>
-    <col min="5" max="5" width="29.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="18.78515625" customWidth="1"/>
+    <col min="3" max="3" width="29.78515625" customWidth="1"/>
+    <col min="4" max="4" width="29.35546875" customWidth="1"/>
+    <col min="5" max="5" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="41.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.92578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
         <v>28</v>
       </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="75" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
         <v>43</v>
       </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
         <v>55</v>
       </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" t="s">
-        <v>25</v>
+      <c r="G20" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -855,50 +1131,50 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10601002\Desktop\AI_topic\_script_backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7149C1C6-037A-4F39-ADE2-8035CA0F6E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EE505D-B325-4302-9449-EBB4B3EB2815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -766,7 +766,7 @@
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="18.78515625" customWidth="1"/>
-    <col min="3" max="3" width="29.78515625" customWidth="1"/>
+    <col min="3" max="3" width="52.5703125" customWidth="1"/>
     <col min="4" max="4" width="29.35546875" customWidth="1"/>
     <col min="5" max="5" width="29.42578125" customWidth="1"/>
     <col min="6" max="6" width="41.5703125" customWidth="1"/>
@@ -908,7 +908,7 @@
       <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>24</v>
       </c>
       <c r="G8" t="s">
@@ -968,7 +968,7 @@
       <c r="C11" t="s">
         <v>25</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>26</v>
       </c>
       <c r="G11" t="s">
@@ -982,7 +982,7 @@
       <c r="C12" t="s">
         <v>27</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>29</v>
       </c>
       <c r="G12" t="s">
@@ -996,7 +996,7 @@
       <c r="C13" t="s">
         <v>28</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>30</v>
       </c>
       <c r="G13" t="s">
@@ -1078,10 +1078,10 @@
       <c r="A18" t="s">
         <v>87</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>59</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>60</v>
       </c>
       <c r="F18" t="s">
@@ -1095,10 +1095,10 @@
       <c r="A19" t="s">
         <v>88</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>48</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>57</v>
       </c>
       <c r="G19" t="s">
@@ -1109,10 +1109,10 @@
       <c r="A20" t="s">
         <v>89</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>54</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>55</v>
       </c>
       <c r="G20" t="s">

--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10601002\Desktop\AI_topic\_script_backup\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10601002\Desktop\AI_topic\_script_backup\單字app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EE505D-B325-4302-9449-EBB4B3EB2815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A9FA58-0A85-4270-9880-7497629CC2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="141">
   <si>
     <t>ID</t>
   </si>
@@ -68,316 +68,505 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>抱怨 n.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>remain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>word</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sentence</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom is off today. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">遵守(規定) v. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">complain 抱怨 v. ; complaint 抱怨 n.; compliance 遵守規定, 符合規定(合規) n. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>compliance  ; [ai]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>complaint  ; [ei]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tom 今天請假。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The power went out.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>停電了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Can I get a Tax refund (for this/these) ? </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you offer Tax-free shopping? </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(這個/些) 我可以退稅嗎?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你們有提供免稅購物嗎? ; (問店家 退稅服務)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寄放行李</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>leave my bags ; hold my bags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Can I leave my bags here?; Can I leave my bags here after check-out?; Can I leave my bags here until 6 PM? </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>other</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>How's it going?; How are you doing?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(正式商務與法規用字, 日常比較常說follow the rules); Please comply with the rules.; 請遵守規則。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>That's all for today.; Let's end the call here.; Thanks, everyone.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(結束電話會議的說法); 今天就到這裡; 我們今天通話就到這裡; 謝謝大家。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>保持 v.; (比較正式, 日常口語較少用)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你好嗎? ; (最近如何? / 你最近好嗎?)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bullets = bullet points (這個黑點看起來像小子彈，所以叫 bullet。)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>happen (口語) ; occur (書面/正式)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我可以把行李放在這裡嗎？; 我(退房後)可以把行李寄放在這裡嗎; 我可以把行李寄存在這裡(到下午6點)嗎？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>phrase</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">What time is breakfast? </t>
+  </si>
+  <si>
+    <t>早餐是幾點？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">What time does breakfast end? </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Can you recommend some good restaurants nearby?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (不限於正式的 restaurant，小吃店、咖啡廳或一般用餐地點都包含在內)</t>
+  </si>
+  <si>
+    <t>我最晚可以幾點來拿行李？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>What's the latest I can pick up my luggage?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">pick up my luggage </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>領取行李</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>What do you recommend?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你推薦什麼？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">早餐幾點結束？(早餐供應到幾點) </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你可以推薦幾間附近不錯的餐廳嗎？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>leave my bags 和 hold my bags 都很口語。;(母語人士通常不會特別區分是背包、旅行袋還是行李箱。; 通常用 luggage 或 bags來統稱行李，很少特別說 suitcase，除非真的要強調是行李箱才用suitcase。)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Are there) any good restaurants nearby?; Any good places to eat nearby?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>附近有沒有什麼不錯的"餐廳"？; 不錯的"地方"可以吃飯？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bullets</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>This issue happens/occurs randomly.</t>
+  </si>
+  <si>
+    <t>happen/occur randomly</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Can you summarize this in bullets?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>English sentence</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>English word</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>這個問題是隨機發生的。</t>
+  </si>
+  <si>
+    <t>隨機發生</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以用條列方式整理嗎？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>條列點、項目符號 (子彈)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Please remain seated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">請保持就座。 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese word</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Good (I'm good), thanks. How about you? ; It's going well.; I'm doing well.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese sentence</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>comply</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>compliance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>complaint</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>howsitgoing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>endcall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dayoff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bullet</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>happenrandom</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>powerwentout</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>taxrefund</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>taxfree</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>recommend_place</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>recommend_restaurant</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>recommend_what</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakfast_time</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakfast_end</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>leave_bags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pickup_luggage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>此產品符合國際標準。</t>
-  </si>
-  <si>
-    <t>抱怨 n.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>remain</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>word</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sentence</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom is off today. </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">遵守(規定) v. </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">complain 抱怨 v. ; complaint 抱怨 n.; compliance 遵守規定, 符合規定(合規) n. </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>compliance  ; [ai]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>complaint  ; [ei]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tom 今天請假。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The power went out.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>停電了。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Can I get a Tax refund (for this/these) ? </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Do you offer Tax-free shopping? </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(這個/些) 我可以退稅嗎?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>你們有提供免稅購物嗎? ; (問店家 退稅服務)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>寄放行李</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>leave my bags ; hold my bags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Can I leave my bags here?; Can I leave my bags here after check-out?; Can I leave my bags here until 6 PM? </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>other</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>How's it going?; How are you doing?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(正式商務與法規用字, 日常比較常說follow the rules); Please comply with the rules.; 請遵守規則。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>That's all for today.; Let's end the call here.; Thanks, everyone.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(結束電話會議的說法); 今天就到這裡; 我們今天通話就到這裡; 謝謝大家。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>保持 v.; (比較正式, 日常口語較少用)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>你好嗎? ; (最近如何? / 你最近好嗎?)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bullets = bullet points (這個黑點看起來像小子彈，所以叫 bullet。)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>happen (口語) ; occur (書面/正式)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>我可以把行李放在這裡嗎？; 我(退房後)可以把行李寄放在這裡嗎; 我可以把行李寄存在這裡(到下午6點)嗎？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>phrase</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">What time is breakfast? </t>
-  </si>
-  <si>
-    <t>早餐是幾點？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">What time does breakfast end? </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Can you recommend some good restaurants nearby?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (不限於正式的 restaurant，小吃店、咖啡廳或一般用餐地點都包含在內)</t>
-  </si>
-  <si>
-    <t>我最晚可以幾點來拿行李？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>What's the latest I can pick up my luggage?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">pick up my luggage </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>領取行李</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>What do you recommend?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>你推薦什麼？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">早餐幾點結束？(早餐供應到幾點) </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>你可以推薦幾間附近不錯的餐廳嗎？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>leave my bags 和 hold my bags 都很口語。;(母語人士通常不會特別區分是背包、旅行袋還是行李箱。; 通常用 luggage 或 bags來統稱行李，很少特別說 suitcase，除非真的要強調是行李箱才用suitcase。)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(Are there) any good restaurants nearby?; Any good places to eat nearby?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>附近有沒有什麼不錯的"餐廳"？; 不錯的"地方"可以吃飯？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bullets</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>This issue happens/occurs randomly.</t>
-  </si>
-  <si>
-    <t>happen/occur randomly</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Can you summarize this in bullets?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>English sentence</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>English word</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>這個問題是隨機發生的。</t>
-  </si>
-  <si>
-    <t>隨機發生</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以用條列方式整理嗎？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>條列點、項目符號 (子彈)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Please remain seated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">請保持就座。 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chinese word</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Good (I'm good), thanks. How about you? ; It's going well.; I'm doing well.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chinese sentence</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>comply</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>compliance</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>complaint</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>howsitgoing</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>endcall</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>dayoff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bullet</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>happenrandom</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>powerwentout</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>taxrefund</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>taxfree</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>recommend_place</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>recommend_restaurant</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>recommend_what</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>breakfast_time</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>breakfast_end</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>leave_bags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pickup_luggage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>搭機</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(把你的) 椅背豎直</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>put your seat upright</t>
+  </si>
+  <si>
+    <t>recline my seat; recline</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(把我的) 椅背往後調; 往後躺/往後傾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>My seat won't recline.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的椅背無法往後調。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Check-in, please. ; I'd like to check in.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我想預訂晚上 7 點、兩位的位子。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我有預約，在Amy Lin名下</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I'd like to make a reservation (book a table) for two at 7 p.m.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>make a reservation; book a table</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>辦理入住，謝謝。; 我要辦理入住</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Do you have any openings today?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I'd like to book a massage for two people at 7 p.m.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我想預約晚上七點、兩位的按摩。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I have an appointment at 7 p.m.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我預約了晚上七點。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>reservation：預留「位置、桌位、房間」; appointment：預約「服務和時間」;餐廳/飯店：I have a reservation.; 按摩、美容、看醫生：I have an appointment.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>預約 (可以用在餐廳訂位/訂房); 預訂桌位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>openings</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空檔 (可以預約的時段)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你今天還有空檔嗎? (可以預約的時段)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Those times don't work for me, but thank you.; Those times don't work for us, so we'll pass. Thanks.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>那些時間對我來說不合適，但謝謝。; 那些時段我們都不方便，所以先不用了，謝謝。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>book a massage; [mer 'saG]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>預約按摩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>have a reservation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>have an appointment</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>checkin_counter</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>reclineseat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>seatupright</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>checkin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bookmassage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>check-in counter; frount desk</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>機場報到櫃檯; 飯店櫃檯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有一個預約 (按摩/看醫生/美容)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有一個預約 (餐廳訂位/飯店訂房)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>havereservation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>makereservation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I have a reservation under Amy Lin.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>haveappointment</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>notworkpass</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>機場報到櫃檯: check-in counter; 
+飯店櫃檯: front desk</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Where is the EVA Air check-in counter? ; Where is the front desk?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>長榮航空的報到櫃台在哪裡？; 飯店櫃檯在哪裡？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>預約</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -461,8 +650,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="VocabularyTable" displayName="VocabularyTable" ref="A1:G20">
-  <autoFilter ref="A1:G20" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="VocabularyTable" displayName="VocabularyTable" ref="A1:G30">
+  <autoFilter ref="A1:G30" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="English word"/>
@@ -761,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -778,19 +967,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -798,27 +987,27 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -827,296 +1016,484 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" t="s">
         <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
         <v>37</v>
       </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
         <v>25</v>
       </c>
-      <c r="E11" t="s">
-        <v>26</v>
-      </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="75" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" t="s">
         <v>43</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
         <v>52</v>
       </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>53</v>
-      </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" t="s">
         <v>45</v>
       </c>
-      <c r="E16" t="s">
-        <v>46</v>
-      </c>
       <c r="G16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" t="s">
         <v>59</v>
       </c>
-      <c r="E18" t="s">
-        <v>60</v>
-      </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" t="s">
         <v>54</v>
       </c>
-      <c r="E20" t="s">
-        <v>55</v>
-      </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" t="s">
+        <v>139</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" t="s">
+        <v>102</v>
+      </c>
+      <c r="G25" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" t="s">
+        <v>109</v>
+      </c>
+      <c r="G27" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="60" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" t="s">
+        <v>118</v>
+      </c>
+      <c r="G30" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
